--- a/results/05_modeling_nested/extra/ALL_summary_extra.xlsx
+++ b/results/05_modeling_nested/extra/ALL_summary_extra.xlsx
@@ -499,14 +499,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gradboost</t>
+          <t>extratrees</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7753054223485613</v>
+        <v>0.7675390063081083</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7871773576552643</v>
+        <v>0.7883998687445136</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -539,10 +539,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8583037287540549</v>
+        <v>0.859008083773802</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7416451769600094</v>
+        <v>0.7371297104138026</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01993688661995984</v>
+        <v>0.02055176014088759</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1154322800342247</v>
+        <v>0.113979645704231</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01432159611287153</v>
+        <v>0.01327209032282319</v>
       </c>
     </row>
     <row r="3">
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7753054223485613</v>
+        <v>0.7645097964865715</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01970127916584561</v>
+        <v>0.01998253139500118</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1352904023718657</v>
+        <v>0.1256960788106765</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01580335909372842</v>
+        <v>0.0111111875630107</v>
       </c>
     </row>
     <row r="4">
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7706431402325833</v>
+        <v>0.7675390063081083</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01824097132401747</v>
+        <v>0.01865128568652915</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1348461163055937</v>
+        <v>0.1342371441199022</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01796663639692724</v>
+        <v>0.01543301317163794</v>
       </c>
     </row>
     <row r="5">
@@ -922,16 +922,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7602130881745923</v>
+        <v>0.7544951316937933</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01392039267849403</v>
+        <v>0.01135738628816723</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1381007774329141</v>
+        <v>0.1182847363702429</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006304980123472345</v>
+        <v>0.00858114579579135</v>
       </c>
     </row>
     <row r="6">
@@ -941,16 +941,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7683861628742591</v>
+        <v>0.7643554917214723</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01822216654225288</v>
+        <v>0.01846287389594341</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1372334173685621</v>
+        <v>0.1308379294871899</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01279874061212412</v>
+        <v>0.01051598906289089</v>
       </c>
     </row>
   </sheetData>
@@ -1001,16 +1001,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.740204074741885</v>
+        <v>0.7423180768872754</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01632377788364275</v>
+        <v>0.01740707860779314</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1504672166943709</v>
+        <v>0.150418939148557</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01174477485781384</v>
+        <v>0.01096860461154251</v>
       </c>
     </row>
     <row r="3">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7871773576552643</v>
+        <v>0.7883998687445136</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01052812384353352</v>
+        <v>0.008023982756139258</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1973119681773526</v>
+        <v>0.1983542113814164</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0126853747689661</v>
+        <v>0.02016621122068829</v>
       </c>
     </row>
     <row r="4">
@@ -1039,16 +1039,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7735862526102607</v>
+        <v>0.7753354867186564</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01355371744243104</v>
+        <v>0.01269043437239893</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1759112725474974</v>
+        <v>0.17448342405062</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009687400006006397</v>
+        <v>0.01082047555388005</v>
       </c>
     </row>
     <row r="5">
@@ -1058,16 +1058,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7524403559136705</v>
+        <v>0.7519759936135035</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01815809526707301</v>
+        <v>0.01897235505529942</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1561432319098676</v>
+        <v>0.1604473928142211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02485627758998294</v>
+        <v>0.02469004502687826</v>
       </c>
     </row>
     <row r="6">
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7729417717062963</v>
+        <v>0.774307977615377</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01696652667544666</v>
+        <v>0.01587442623235423</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1942662352121397</v>
+        <v>0.1950261679377055</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01901994907284056</v>
+        <v>0.01799920717845304</v>
       </c>
     </row>
   </sheetData>
@@ -1137,16 +1137,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8380082807867801</v>
+        <v>0.8384060741259433</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02096671842468235</v>
+        <v>0.02144293790929938</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3626783404222963</v>
+        <v>0.3621556760174849</v>
       </c>
       <c r="E2" t="n">
-        <v>0.036706105017073</v>
+        <v>0.03892340905464424</v>
       </c>
     </row>
     <row r="3">
@@ -1156,16 +1156,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8574353556750157</v>
+        <v>0.8560991058465504</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01799383944150814</v>
+        <v>0.01482657545051336</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3886767546878503</v>
+        <v>0.39299150315043</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03992927212471939</v>
+        <v>0.04328364565501456</v>
       </c>
     </row>
     <row r="4">
@@ -1175,16 +1175,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8565860138008118</v>
+        <v>0.8581412102778174</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01338845306581416</v>
+        <v>0.01343351241384613</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3853073807126989</v>
+        <v>0.3894527575943291</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04225413424787459</v>
+        <v>0.04159488439462301</v>
       </c>
     </row>
     <row r="5">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8352441775362471</v>
+        <v>0.8341393621732202</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0196280256658652</v>
+        <v>0.0194148298495687</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2894366220528332</v>
+        <v>0.28501264267978</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02287044597953614</v>
+        <v>0.02798555356943055</v>
       </c>
     </row>
     <row r="6">
@@ -1213,16 +1213,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8583037287540549</v>
+        <v>0.859008083773802</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01749714474713204</v>
+        <v>0.01775204446314711</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3999103855990315</v>
+        <v>0.4019031011699147</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04408977752764391</v>
+        <v>0.05002623507853219</v>
       </c>
     </row>
   </sheetData>
